--- a/artfynd/A 57233-2025 artfynd.xlsx
+++ b/artfynd/A 57233-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125781668</v>
+        <v>227048</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jåvan, Ly lm</t>
+          <t>Brattmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622633</v>
+        <v>622795</v>
       </c>
       <c r="R2" t="n">
-        <v>7195204</v>
+        <v>7194690</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -740,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2007-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2007-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,64 +756,80 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Hans Sundström, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125781645</v>
+        <v>125754190</v>
       </c>
       <c r="B3" t="n">
-        <v>80109</v>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jovan, Ly lm</t>
+          <t>Björnberget, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622628</v>
+        <v>622577</v>
       </c>
       <c r="R3" t="n">
-        <v>7195184</v>
+        <v>7195134</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,95 +856,78 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831582</v>
+        <v>125781668</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jovan, Ly lm</t>
+          <t>Jåvan, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622719</v>
+        <v>622633</v>
       </c>
       <c r="R4" t="n">
-        <v>7195094</v>
+        <v>7195204</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,9 +954,19 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,15 +981,440 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125781645</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jovan, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>622628</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7195184</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125831582</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jovan, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>622719</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7195094</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103785201</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnberget, Jovan EP, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>622854</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7194573</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125781630</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jovan, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>622575</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7195132</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
